--- a/artfynd/A 20788-2024 artfynd.xlsx
+++ b/artfynd/A 20788-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY90"/>
+  <dimension ref="A1:AY89"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -8502,7 +8502,7 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>101778463</v>
+        <v>101778274</v>
       </c>
       <c r="B65" t="n">
         <v>96334</v>
@@ -8535,7 +8535,11 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I65" t="inlineStr"/>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr">
         <is>
           <t>plantor/tuvor</t>
@@ -8547,17 +8551,16 @@
         </is>
       </c>
       <c r="L65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
           <t>Avesta, Dlr</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>568188.9969459451</v>
+        <v>568212.8489382822</v>
       </c>
       <c r="R65" t="n">
-        <v>6676415.886692976</v>
+        <v>6676418.319650487</v>
       </c>
       <c r="S65" t="n">
         <v>25</v>
@@ -8589,7 +8592,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>19:46</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -8599,12 +8602,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>19:46</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ca ett hundratal plantor</t>
+          <t>19:39</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -8613,7 +8611,6 @@
       <c r="AE65" t="b">
         <v>0</v>
       </c>
-      <c r="AF65" t="inlineStr"/>
       <c r="AG65" t="b">
         <v>0</v>
       </c>
@@ -8632,7 +8629,7 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>101778274</v>
+        <v>101776184</v>
       </c>
       <c r="B66" t="n">
         <v>96334</v>
@@ -8665,21 +8662,8 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="J66" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+      <c r="I66" t="inlineStr"/>
+      <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
@@ -8687,10 +8671,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>568212.8489382822</v>
+        <v>568112.3519256779</v>
       </c>
       <c r="R66" t="n">
-        <v>6676418.319650487</v>
+        <v>6676548.15843135</v>
       </c>
       <c r="S66" t="n">
         <v>25</v>
@@ -8722,7 +8706,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -8732,7 +8716,7 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>19:39</t>
+          <t>18:19</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -8747,19 +8731,19 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Annelie Hilmerby</t>
+          <t>Philipp Weiss</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>101776184</v>
+        <v>101777076</v>
       </c>
       <c r="B67" t="n">
         <v>96334</v>
@@ -8801,10 +8785,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>568112.3519256779</v>
+        <v>568155.4296304646</v>
       </c>
       <c r="R67" t="n">
-        <v>6676548.15843135</v>
+        <v>6676320.325979673</v>
       </c>
       <c r="S67" t="n">
         <v>25</v>
@@ -8836,7 +8820,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -8846,7 +8830,7 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:19</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -8873,7 +8857,7 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>101777076</v>
+        <v>101776569</v>
       </c>
       <c r="B68" t="n">
         <v>96334</v>
@@ -8906,7 +8890,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I68" t="inlineStr"/>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
+      <c r="J68" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K68" t="inlineStr"/>
       <c r="L68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
@@ -8915,10 +8908,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>568155.4296304646</v>
+        <v>568241.7307485789</v>
       </c>
       <c r="R68" t="n">
-        <v>6676320.325979673</v>
+        <v>6676524.725485561</v>
       </c>
       <c r="S68" t="n">
         <v>25</v>
@@ -8950,7 +8943,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -8960,7 +8953,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:36</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8987,7 +8980,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>101776569</v>
+        <v>101776808</v>
       </c>
       <c r="B69" t="n">
         <v>96334</v>
@@ -9022,7 +9015,7 @@
       </c>
       <c r="I69" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>100</t>
         </is>
       </c>
       <c r="J69" t="inlineStr">
@@ -9038,10 +9031,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>568241.7307485789</v>
+        <v>568220.6414828579</v>
       </c>
       <c r="R69" t="n">
-        <v>6676524.725485561</v>
+        <v>6676374.228598825</v>
       </c>
       <c r="S69" t="n">
         <v>25</v>
@@ -9073,7 +9066,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -9083,7 +9076,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>18:36</t>
+          <t>18:46</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -9110,7 +9103,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>101776808</v>
+        <v>101779024</v>
       </c>
       <c r="B70" t="n">
         <v>96334</v>
@@ -9143,16 +9136,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J70" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
@@ -9161,10 +9145,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>568220.6414828579</v>
+        <v>568127.1557440435</v>
       </c>
       <c r="R70" t="n">
-        <v>6676374.228598825</v>
+        <v>6676742.265771645</v>
       </c>
       <c r="S70" t="n">
         <v>25</v>
@@ -9196,7 +9180,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -9206,7 +9190,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:46</t>
+          <t>20:07</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -9233,7 +9217,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>101779024</v>
+        <v>101778773</v>
       </c>
       <c r="B71" t="n">
         <v>96334</v>
@@ -9275,10 +9259,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>568127.1557440435</v>
+        <v>568432.4714671583</v>
       </c>
       <c r="R71" t="n">
-        <v>6676742.265771645</v>
+        <v>6676680.872344309</v>
       </c>
       <c r="S71" t="n">
         <v>25</v>
@@ -9310,7 +9294,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -9320,7 +9304,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>20:07</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -9347,7 +9331,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>101778773</v>
+        <v>101776785</v>
       </c>
       <c r="B72" t="n">
         <v>96334</v>
@@ -9389,10 +9373,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>568432.4714671583</v>
+        <v>568233.2663472353</v>
       </c>
       <c r="R72" t="n">
-        <v>6676680.872344309</v>
+        <v>6676391.363492764</v>
       </c>
       <c r="S72" t="n">
         <v>25</v>
@@ -9424,7 +9408,7 @@
       </c>
       <c r="Z72" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
@@ -9434,7 +9418,7 @@
       </c>
       <c r="AB72" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>18:45</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -9461,7 +9445,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>101776785</v>
+        <v>101776555</v>
       </c>
       <c r="B73" t="n">
         <v>96334</v>
@@ -9494,8 +9478,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J73" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K73" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
@@ -9503,10 +9500,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>568233.2663472353</v>
+        <v>568248.5683693575</v>
       </c>
       <c r="R73" t="n">
-        <v>6676391.363492764</v>
+        <v>6676531.811376506</v>
       </c>
       <c r="S73" t="n">
         <v>25</v>
@@ -9538,7 +9535,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -9548,7 +9545,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>18:45</t>
+          <t>18:35</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -9575,7 +9572,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>101776555</v>
+        <v>101776452</v>
       </c>
       <c r="B74" t="n">
         <v>96334</v>
@@ -9610,7 +9607,7 @@
       </c>
       <c r="I74" t="inlineStr">
         <is>
-          <t>100</t>
+          <t>45</t>
         </is>
       </c>
       <c r="J74" t="inlineStr">
@@ -9618,11 +9615,7 @@
           <t>plantor/tuvor</t>
         </is>
       </c>
-      <c r="K74" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K74" t="inlineStr"/>
       <c r="L74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
@@ -9630,10 +9623,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>568248.5683693575</v>
+        <v>568261.5169756592</v>
       </c>
       <c r="R74" t="n">
-        <v>6676531.811376506</v>
+        <v>6676611.575423738</v>
       </c>
       <c r="S74" t="n">
         <v>25</v>
@@ -9665,7 +9658,7 @@
       </c>
       <c r="Z74" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
@@ -9675,7 +9668,7 @@
       </c>
       <c r="AB74" t="inlineStr">
         <is>
-          <t>18:35</t>
+          <t>18:27</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -9702,7 +9695,7 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>101776452</v>
+        <v>101776907</v>
       </c>
       <c r="B75" t="n">
         <v>96334</v>
@@ -9735,16 +9728,7 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="J75" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
@@ -9753,10 +9737,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>568261.5169756592</v>
+        <v>568181.9720454739</v>
       </c>
       <c r="R75" t="n">
-        <v>6676611.575423738</v>
+        <v>6676338.714413191</v>
       </c>
       <c r="S75" t="n">
         <v>25</v>
@@ -9788,7 +9772,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -9798,7 +9782,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>18:27</t>
+          <t>18:50</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -9825,7 +9809,7 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>101776907</v>
+        <v>101776020</v>
       </c>
       <c r="B76" t="n">
         <v>96334</v>
@@ -9867,10 +9851,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>568181.9720454739</v>
+        <v>568018.5823871772</v>
       </c>
       <c r="R76" t="n">
-        <v>6676338.714413191</v>
+        <v>6676637.863065535</v>
       </c>
       <c r="S76" t="n">
         <v>25</v>
@@ -9902,7 +9886,7 @@
       </c>
       <c r="Z76" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
@@ -9912,7 +9896,7 @@
       </c>
       <c r="AB76" t="inlineStr">
         <is>
-          <t>18:50</t>
+          <t>18:14</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -9939,7 +9923,7 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>101776020</v>
+        <v>101778582</v>
       </c>
       <c r="B77" t="n">
         <v>96334</v>
@@ -9981,10 +9965,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>568018.5823871772</v>
+        <v>568341.6313027216</v>
       </c>
       <c r="R77" t="n">
-        <v>6676637.863065535</v>
+        <v>6676613.568797009</v>
       </c>
       <c r="S77" t="n">
         <v>25</v>
@@ -10016,7 +10000,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -10026,7 +10010,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>18:14</t>
+          <t>19:50</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -10053,7 +10037,7 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>101778582</v>
+        <v>101778709</v>
       </c>
       <c r="B78" t="n">
         <v>96334</v>
@@ -10095,10 +10079,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>568341.6313027216</v>
+        <v>568357.1849909758</v>
       </c>
       <c r="R78" t="n">
-        <v>6676613.568797009</v>
+        <v>6676633.739842963</v>
       </c>
       <c r="S78" t="n">
         <v>25</v>
@@ -10130,7 +10114,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -10140,7 +10124,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>19:50</t>
+          <t>19:54</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -10167,7 +10151,7 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>101778709</v>
+        <v>101779127</v>
       </c>
       <c r="B79" t="n">
         <v>96334</v>
@@ -10209,10 +10193,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>568357.1849909758</v>
+        <v>568048.3120349532</v>
       </c>
       <c r="R79" t="n">
-        <v>6676633.739842963</v>
+        <v>6676805.90288205</v>
       </c>
       <c r="S79" t="n">
         <v>25</v>
@@ -10244,7 +10228,7 @@
       </c>
       <c r="Z79" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AA79" t="inlineStr">
@@ -10254,7 +10238,7 @@
       </c>
       <c r="AB79" t="inlineStr">
         <is>
-          <t>19:54</t>
+          <t>20:10</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -10281,7 +10265,7 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>101779127</v>
+        <v>101778738</v>
       </c>
       <c r="B80" t="n">
         <v>96334</v>
@@ -10323,10 +10307,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>568048.3120349532</v>
+        <v>568383.2636224383</v>
       </c>
       <c r="R80" t="n">
-        <v>6676805.90288205</v>
+        <v>6676650.131620801</v>
       </c>
       <c r="S80" t="n">
         <v>25</v>
@@ -10358,7 +10342,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -10368,7 +10352,7 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>20:10</t>
+          <t>19:55</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -10395,10 +10379,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>101778738</v>
+        <v>101777070</v>
       </c>
       <c r="B81" t="n">
-        <v>96334</v>
+        <v>103265</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -10407,29 +10391,33 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>221144</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>Sw.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
-      <c r="K81" t="inlineStr"/>
+      <c r="K81" t="inlineStr">
+        <is>
+          <t>blomknopp</t>
+        </is>
+      </c>
       <c r="L81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
@@ -10437,10 +10425,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>568383.2636224383</v>
+        <v>568155.4296304646</v>
       </c>
       <c r="R81" t="n">
-        <v>6676650.131620801</v>
+        <v>6676320.325979673</v>
       </c>
       <c r="S81" t="n">
         <v>25</v>
@@ -10472,7 +10460,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -10482,7 +10470,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>19:55</t>
+          <t>18:55</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -10509,10 +10497,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>101777070</v>
+        <v>101776047</v>
       </c>
       <c r="B82" t="n">
-        <v>103265</v>
+        <v>96334</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -10521,33 +10509,29 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>blomknopp</t>
-        </is>
-      </c>
+      <c r="K82" t="inlineStr"/>
       <c r="L82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
@@ -10555,10 +10539,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>568155.4296304646</v>
+        <v>568037.724508332</v>
       </c>
       <c r="R82" t="n">
-        <v>6676320.325979673</v>
+        <v>6676625.794038202</v>
       </c>
       <c r="S82" t="n">
         <v>25</v>
@@ -10590,7 +10574,7 @@
       </c>
       <c r="Z82" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
@@ -10600,7 +10584,7 @@
       </c>
       <c r="AB82" t="inlineStr">
         <is>
-          <t>18:55</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -10627,7 +10611,7 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>101776047</v>
+        <v>101776631</v>
       </c>
       <c r="B83" t="n">
         <v>96334</v>
@@ -10669,10 +10653,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>568037.724508332</v>
+        <v>568231.8079964163</v>
       </c>
       <c r="R83" t="n">
-        <v>6676625.794038202</v>
+        <v>6676496.2100244</v>
       </c>
       <c r="S83" t="n">
         <v>25</v>
@@ -10704,7 +10688,7 @@
       </c>
       <c r="Z83" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AA83" t="inlineStr">
@@ -10714,7 +10698,7 @@
       </c>
       <c r="AB83" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:39</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -10741,7 +10725,7 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>101776631</v>
+        <v>101777296</v>
       </c>
       <c r="B84" t="n">
         <v>96334</v>
@@ -10783,10 +10767,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>568231.8079964163</v>
+        <v>568113.0046721599</v>
       </c>
       <c r="R84" t="n">
-        <v>6676496.2100244</v>
+        <v>6676325.997217036</v>
       </c>
       <c r="S84" t="n">
         <v>25</v>
@@ -10818,7 +10802,7 @@
       </c>
       <c r="Z84" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AA84" t="inlineStr">
@@ -10828,7 +10812,7 @@
       </c>
       <c r="AB84" t="inlineStr">
         <is>
-          <t>18:39</t>
+          <t>19:01</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -10855,7 +10839,7 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>101777296</v>
+        <v>101777347</v>
       </c>
       <c r="B85" t="n">
         <v>96334</v>
@@ -10897,10 +10881,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>568113.0046721599</v>
+        <v>568132.2996089906</v>
       </c>
       <c r="R85" t="n">
-        <v>6676325.997217036</v>
+        <v>6676386.001809584</v>
       </c>
       <c r="S85" t="n">
         <v>25</v>
@@ -10932,7 +10916,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -10942,7 +10926,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:01</t>
+          <t>19:04</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -10969,7 +10953,7 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>101777347</v>
+        <v>101778862</v>
       </c>
       <c r="B86" t="n">
         <v>96334</v>
@@ -11011,10 +10995,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>568132.2996089906</v>
+        <v>568320.9528341276</v>
       </c>
       <c r="R86" t="n">
-        <v>6676386.001809584</v>
+        <v>6676734.450726002</v>
       </c>
       <c r="S86" t="n">
         <v>25</v>
@@ -11046,7 +11030,7 @@
       </c>
       <c r="Z86" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
@@ -11056,7 +11040,7 @@
       </c>
       <c r="AB86" t="inlineStr">
         <is>
-          <t>19:04</t>
+          <t>20:01</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -11083,7 +11067,7 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>101778862</v>
+        <v>101778784</v>
       </c>
       <c r="B87" t="n">
         <v>96334</v>
@@ -11125,10 +11109,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>568320.9528341276</v>
+        <v>568410.6490933634</v>
       </c>
       <c r="R87" t="n">
-        <v>6676734.450726002</v>
+        <v>6676676.488013214</v>
       </c>
       <c r="S87" t="n">
         <v>25</v>
@@ -11160,7 +11144,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -11170,7 +11154,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>20:01</t>
+          <t>19:57</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -11197,7 +11181,7 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>101778784</v>
+        <v>101776759</v>
       </c>
       <c r="B88" t="n">
         <v>96334</v>
@@ -11230,7 +11214,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr"/>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K88" t="inlineStr"/>
       <c r="L88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
@@ -11239,10 +11232,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>568410.6490933634</v>
+        <v>568248.8586867169</v>
       </c>
       <c r="R88" t="n">
-        <v>6676676.488013214</v>
+        <v>6676409.547806908</v>
       </c>
       <c r="S88" t="n">
         <v>25</v>
@@ -11274,7 +11267,7 @@
       </c>
       <c r="Z88" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
@@ -11284,7 +11277,7 @@
       </c>
       <c r="AB88" t="inlineStr">
         <is>
-          <t>19:57</t>
+          <t>18:44</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -11311,7 +11304,7 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>101776759</v>
+        <v>101777577</v>
       </c>
       <c r="B89" t="n">
         <v>96334</v>
@@ -11362,10 +11355,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>568248.8586867169</v>
+        <v>568177.2747200509</v>
       </c>
       <c r="R89" t="n">
-        <v>6676409.547806908</v>
+        <v>6676403.739272519</v>
       </c>
       <c r="S89" t="n">
         <v>25</v>
@@ -11397,7 +11390,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -11407,7 +11400,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>18:44</t>
+          <t>19:12</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -11431,129 +11424,6 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
-    </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>101777577</v>
-      </c>
-      <c r="B90" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D90" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E90" t="n">
-        <v>220787</v>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>Knärot</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>Goodyera repens</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr">
-        <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="P90" t="inlineStr">
-        <is>
-          <t>Avesta, Dlr</t>
-        </is>
-      </c>
-      <c r="Q90" t="n">
-        <v>568177.2747200509</v>
-      </c>
-      <c r="R90" t="n">
-        <v>6676403.739272519</v>
-      </c>
-      <c r="S90" t="n">
-        <v>25</v>
-      </c>
-      <c r="T90" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="U90" t="inlineStr">
-        <is>
-          <t>Avesta</t>
-        </is>
-      </c>
-      <c r="V90" t="inlineStr">
-        <is>
-          <t>Dalarna</t>
-        </is>
-      </c>
-      <c r="W90" t="inlineStr">
-        <is>
-          <t>Folkärna</t>
-        </is>
-      </c>
-      <c r="Y90" t="inlineStr">
-        <is>
-          <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
-      <c r="AA90" t="inlineStr">
-        <is>
-          <t>2022-06-20</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>19:12</t>
-        </is>
-      </c>
-      <c r="AD90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG90" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT90" t="inlineStr"/>
-      <c r="AW90" t="inlineStr">
-        <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AX90" t="inlineStr">
-        <is>
-          <t>Philipp Weiss</t>
-        </is>
-      </c>
-      <c r="AY90" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
